--- a/data/trans_bre/P57_AF_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,6</t>
+          <t>-4,33; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,45</t>
+          <t>1,18; 11,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,39</t>
+          <t>-0,36; 8,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 9,97</t>
+          <t>-0,09; 9,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 8,74</t>
+          <t>-6,29; 8,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 21,84</t>
+          <t>2,08; 22,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 11,82</t>
+          <t>-0,51; 12,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 21,03</t>
+          <t>-0,16; 21,44</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,25</t>
+          <t>-2,35; 6,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,72</t>
+          <t>0,89; 9,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 7,18</t>
+          <t>-0,26; 7,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 38,25</t>
+          <t>1,94; 37,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 12,58</t>
+          <t>-3,95; 10,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 18,0</t>
+          <t>1,35; 16,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 10,06</t>
+          <t>-0,37; 10,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 160,91</t>
+          <t>3,28; 151,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 6,63</t>
+          <t>-4,36; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 7,91</t>
+          <t>-2,54; 7,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,19</t>
+          <t>-2,55; 5,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 24,08</t>
+          <t>-6,77; 27,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 12,29</t>
+          <t>-7,34; 13,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 13,73</t>
+          <t>-4,1; 13,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,6</t>
+          <t>-3,07; 7,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 43,62</t>
+          <t>-10,99; 48,9</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 2,85</t>
+          <t>-5,55; 2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,08</t>
+          <t>0,12; 8,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,04</t>
+          <t>-3,85; 4,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,34</t>
+          <t>-13,25; 2,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 4,99</t>
+          <t>-8,94; 5,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 14,04</t>
+          <t>0,2; 13,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 7,52</t>
+          <t>-5,38; 7,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 4,29</t>
+          <t>-24,17; 4,15</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,99</t>
+          <t>-1,92; 3,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,32</t>
+          <t>2,54; 7,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,3</t>
+          <t>0,08; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 19,88</t>
+          <t>0,3; 19,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,02</t>
+          <t>-3,07; 5,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 12,06</t>
+          <t>3,96; 12,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,9</t>
+          <t>0,1; 5,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 47,02</t>
+          <t>0,67; 43,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AF_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 5,55</t>
+          <t>-4,42; 5,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,91</t>
+          <t>0,64; 11,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,83</t>
+          <t>-0,81; 8,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 9,96</t>
+          <t>-1,85; 8,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 8,61</t>
+          <t>-6,37; 9,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 22,04</t>
+          <t>1,03; 21,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 12,46</t>
+          <t>-1,04; 12,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 21,44</t>
+          <t>-3,17; 17,41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,47</t>
+          <t>-2,52; 6,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,69</t>
+          <t>1,51; 10,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 7,39</t>
+          <t>-0,66; 7,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 37,43</t>
+          <t>0,23; 8,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 10,97</t>
+          <t>-4,07; 11,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 16,08</t>
+          <t>2,31; 16,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 10,43</t>
+          <t>-0,83; 10,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 151,61</t>
+          <t>0,34; 16,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>-4,01%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 7,06</t>
+          <t>-4,01; 6,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,78</t>
+          <t>-2,34; 8,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 5,51</t>
+          <t>-3,13; 5,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 27,12</t>
+          <t>-7,5; 2,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 13,08</t>
+          <t>-6,89; 11,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 13,97</t>
+          <t>-3,84; 14,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,05</t>
+          <t>-3,8; 6,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 48,9</t>
+          <t>-11,83; 4,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,46</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,3%</t>
+          <t>-0,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 2,96</t>
+          <t>-5,92; 3,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,71</t>
+          <t>0,09; 8,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,79</t>
+          <t>-3,86; 4,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 2,22</t>
+          <t>-4,77; 4,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 5,17</t>
+          <t>-9,74; 5,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 13,29</t>
+          <t>0,11; 13,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 7,22</t>
+          <t>-5,38; 7,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 4,15</t>
+          <t>-8,06; 7,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,05</t>
+          <t>-1,87; 3,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,36</t>
+          <t>2,64; 7,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,17</t>
+          <t>0,05; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 19,56</t>
+          <t>-1,28; 3,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,14</t>
+          <t>-3,0; 5,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 12,19</t>
+          <t>4,16; 12,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,7</t>
+          <t>0,07; 5,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 43,49</t>
+          <t>-2,16; 6,37</t>
         </is>
       </c>
     </row>
